--- a/test_data/master_test.xlsx
+++ b/test_data/master_test.xlsx
@@ -428,12 +428,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Short description</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Primary CI/Application</t>
+          <t>Configuration Item</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/test_data/master_test.xlsx
+++ b/test_data/master_test.xlsx
@@ -428,12 +428,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Configuration Item</t>
+          <t>Primary CI/Application</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/test_data/master_test.xlsx
+++ b/test_data/master_test.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidated" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Lookup" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
